--- a/Output_2026/SAAM_Part1_EUR_results.xlsx
+++ b/Output_2026/SAAM_Part1_EUR_results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,30 +427,35 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Ann. Return (%)</t>
+          <t>Ann. Return Arith. (%)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Ann. Return Geom. (%)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Ann. Vol (%)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Min Mo. (%)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Max Mo. (%)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Max DD (%)</t>
         </is>
@@ -463,21 +468,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.5</v>
+        <v>8.19</v>
       </c>
       <c r="C2" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="D2" t="n">
         <v>15.87</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.526</v>
-      </c>
       <c r="E2" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="F2" t="n">
         <v>-15.34</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>18.27</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>-28.17</v>
       </c>
     </row>
@@ -488,21 +496,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="C3" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="D3" t="n">
         <v>13.92</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.278</v>
-      </c>
       <c r="E3" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="F3" t="n">
         <v>-12.02</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>14.28</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>-24.46</v>
       </c>
     </row>

--- a/Output_2026/SAAM_Part1_EUR_results.xlsx
+++ b/Output_2026/SAAM_Part1_EUR_results.xlsx
@@ -427,17 +427,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Ann. Return Arith. (%)</t>
+          <t>Ann Ret Arith (%)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Ann. Return Geom. (%)</t>
+          <t>Ann Ret Geom (%)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Ann. Vol (%)</t>
+          <t>Ann Vol (%)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -447,12 +447,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Min Mo. (%)</t>
+          <t>Min Mo (%)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Max Mo. (%)</t>
+          <t>Max Mo (%)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -464,7 +464,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Val-Wgt P^(vw)</t>
+          <t>Value-Weighted</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -492,7 +492,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Min-Var P_oos^(mv)</t>
+          <t>Min-Variance</t>
         </is>
       </c>
       <c r="B3" t="n">
